--- a/sim_proj_updated/severity_ranking.xlsx
+++ b/sim_proj_updated/severity_ranking.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="88" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="110" uniqueCount="27">
   <si>
     <t>Parameter</t>
   </si>
@@ -79,6 +79,21 @@
   </si>
   <si>
     <t>MaxExceedance</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Coliform</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>E. coli</t>
   </si>
 </sst>
 </file>
@@ -167,7 +182,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0">
         <v>352.69999999999999</v>
@@ -178,7 +193,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B5" s="0">
         <v>333.33333333333331</v>
@@ -200,7 +215,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B7" s="0">
         <v>263.02222222222218</v>
@@ -222,57 +237,57 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="0">
-        <v>206.51111111111112</v>
+        <v>193.34722222222223</v>
       </c>
       <c r="C9" s="0">
-        <v>324</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="0">
-        <v>193.34722222222223</v>
+        <v>192.84444444444443</v>
       </c>
       <c r="C10" s="0">
-        <v>299.5</v>
+        <v>390.66666666666669</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="0">
-        <v>192.84444444444443</v>
+        <v>131.66666666666666</v>
       </c>
       <c r="C11" s="0">
-        <v>390.66666666666669</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="0">
-        <v>131.66666666666666</v>
+        <v>83.078703703703709</v>
       </c>
       <c r="C12" s="0">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B13" s="0">
-        <v>83.078703703703709</v>
+        <v>53.255555555555553</v>
       </c>
       <c r="C13" s="0">
-        <v>150</v>
+        <v>112.00000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -299,7 +314,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B16" s="0">
         <v>0</v>
@@ -343,7 +358,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B20" s="0">
         <v>0</v>
